--- a/backend/docusense_reports/DBCE-ECS-SEM-V_OCR_EXTRACTED.xlsx
+++ b/backend/docusense_reports/DBCE-ECS-SEM-V_OCR_EXTRACTED.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cloyr\Desktop\EduSphere Project\backend\docusense_reports\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70FD2613-B864-497E-8C0B-A6E047D8070A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -199,169 +205,169 @@
     <t>50416</t>
   </si>
   <si>
-    <t>ADITI SANDESH VADKAR Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>ASHTON REMIGIO DSOUZA Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>AYUSH ASHOK NAGARSEKAR Paper Paper  Paper Theory IA Code Credits ECS</t>
-  </si>
-  <si>
-    <t>BHAVANA C. PUROHIT Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>BRIJESH KISHOR NAIK DESSAI Paper Paper  Paper Theory IA Code Credits ECS</t>
-  </si>
-  <si>
-    <t>CLOY FRANSTER RODRIGUES Paper Paper  Paper Theory Code Credits ECSS</t>
-  </si>
-  <si>
-    <t>DISHA SAMID TALAULIKAR Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>GABINAZ ESTHER DO ROSARIO PIRES Paper Paper  Paper Theory Term Code Credits Work ECS</t>
-  </si>
-  <si>
-    <t>GAVIN D CUNHA Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>GILES HAYDEN BORGES Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>HRISHIKESH DINESH NAIK Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>HRISHIKESH RAMESH BHAVE Paper Paper  Paper Theory IA Code Credits ECS</t>
-  </si>
-  <si>
-    <t>IVAN MARIO DOMINGOS TRAVASSOS Paper Paper  Paper Theory IA Term Code Credits Work ECS</t>
-  </si>
-  <si>
-    <t>JEMIMA DSOUZA Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>JOSHUA NEIL CASTELLO Paper Paper  Paper Theory Code Credits ECSS</t>
-  </si>
-  <si>
-    <t>KINSEL MONTEIRO Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>LENOY MENEZES Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>LOXLEY LIGORIO DIAS Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>MARYANN BEVERLY COUTINHO Paper Paper  Paper Theory IA Code Credits ECS</t>
-  </si>
-  <si>
-    <t>MAYURESH SUJAY PATIL Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>MEHULKUMAR MAHESHKUMAR PRASAD Paper Paper  Paper Theory Term Code Credits Work ECS</t>
-  </si>
-  <si>
-    <t>MOHAMMED SHAMSHUDDIN SHAIKH Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>MYRUS ANSLEY RODRIGUES Paper Paper  Paper Theory IA Term Theory Practical Oral Total Grade Weighted Code Grade Credits Work Total Grade Point Points ECS</t>
-  </si>
-  <si>
-    <t>NAGESH RAJESH PRABHU Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>OM VELU NAIDU Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>PRATIK DILIP BORKAR Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>RAOUL TEOFILO DO ROSARIO VAS Paper Paper  Paper Theory IA Term Theory Practical Oral Total Code Credits Work Total ECSSTO Electronic Communication Systems</t>
-  </si>
-  <si>
-    <t>REAIAH SHALOM FERNANDES Paper Paper  Paper Theory IA Term Theory Practical Oral Total Grade Weighted Code Grade Credits Work Total Grade Point Points ECS</t>
-  </si>
-  <si>
-    <t>REEVE ALBERT RODRIGUES Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>REUBEN VALES Paper Paper  Paper Theory Code Credits ECSS</t>
-  </si>
-  <si>
-    <t>RHEA CLAIRE FERNANDES Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>RIDHIMA ROSHAN VERNEKAR Paper Paper  Paper Theory IA Code Credits ECS</t>
-  </si>
-  <si>
-    <t>RIGEL SAMUEL FERNANDES Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>RIYA MARUTI KALAL Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>ROHIDAS MANIKRAO RAIKAR Paper Paper  Paper Theory IA Term Theory Practical Oral Total Code Credits Work Total ECS</t>
-  </si>
-  <si>
-    <t>RUCHA KASHINATH SAWANT Paper Paper  Paper Theory IA Code Credits ECS</t>
-  </si>
-  <si>
-    <t>SALVA SAYAD Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>SANIL PRAKASH NAIK Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>SAUMYA VIKAS SHENVI MAUZEKAR Paper Paper  Paper Theory IA Code Credits ECS</t>
-  </si>
-  <si>
-    <t>SHAWN STANTON DCOSTA Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>SHEEHAN RAPHAEL SA Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>SHIVAM CHOUHAN Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>SHOUNAK SURAJ VELIP Paper Paper Mame Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>SHRAVANI RANJIT DHERE Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>SHREYA GOVIND JOSHI Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>SPARSH VISHAL ALVE Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>TABREJ ABUBAKKAR AGASNALI Paper Paper  Paper Theory IA Term Theory Practical Oral Total Code Credits Work Total ECS</t>
-  </si>
-  <si>
-    <t>TANISH SANJIV LOTLICAR Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>TROY PRESTON FERNANDES Paper Paper  Paper Theory IA Code Credits ECS</t>
-  </si>
-  <si>
-    <t>UTKARSHA UMESH TAKER Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>VANOSH CARL OZORIO FERNANDES Paper Paper  Paper Theory IA Code Credits ECS</t>
-  </si>
-  <si>
-    <t>VANSHIKA GUPTA Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>VIHAAN VISHAL NAIK KARMALI Paper Paper Namie Paper Theory IA Code Credits ECS</t>
-  </si>
-  <si>
-    <t>VRAJ ROSHAN POROB Paper Paper  Paper Theory Code Credits ECS</t>
-  </si>
-  <si>
-    <t>YASH ANAND SURLEKAR Paper Paper  Paper Theory Code Credits ECS</t>
+    <t>ADITI SANDESH VADKAR</t>
+  </si>
+  <si>
+    <t>ASHTON REMIGIO DSOUZA</t>
+  </si>
+  <si>
+    <t>AYUSH ASHOK NAGARSEKAR</t>
+  </si>
+  <si>
+    <t>BHAVANA C. PUROHIT</t>
+  </si>
+  <si>
+    <t>BRIJESH KISHOR NAIK DESSAI</t>
+  </si>
+  <si>
+    <t>CLOY FRANSTER RODRIGUES</t>
+  </si>
+  <si>
+    <t>DISHA SAMID TALAULIKAR</t>
+  </si>
+  <si>
+    <t>GABINAZ ESTHER DO ROSARIO PIRES</t>
+  </si>
+  <si>
+    <t>GAVIN D CUNHA</t>
+  </si>
+  <si>
+    <t>GILES HAYDEN BORGES</t>
+  </si>
+  <si>
+    <t>HRISHIKESH DINESH NAIK</t>
+  </si>
+  <si>
+    <t>HRISHIKESH RAMESH BHAVE</t>
+  </si>
+  <si>
+    <t>IVAN MARIO DOMINGOS TRAVASSOS</t>
+  </si>
+  <si>
+    <t>JEMIMA DSOUZA</t>
+  </si>
+  <si>
+    <t>JOSHUA NEIL CASTELLO</t>
+  </si>
+  <si>
+    <t>KINSEL MONTEIRO</t>
+  </si>
+  <si>
+    <t>LENOY MENEZES</t>
+  </si>
+  <si>
+    <t>LOXLEY LIGORIO DIAS</t>
+  </si>
+  <si>
+    <t>MARYANN BEVERLY COUTINHO</t>
+  </si>
+  <si>
+    <t>MAYURESH SUJAY PATIL</t>
+  </si>
+  <si>
+    <t>MEHULKUMAR MAHESHKUMAR</t>
+  </si>
+  <si>
+    <t>MOHAMMED SHAMSHUDDIN SHAIKH</t>
+  </si>
+  <si>
+    <t>MYRUS ANSLEY RODRIGUES</t>
+  </si>
+  <si>
+    <t>NAGESH RAJESH</t>
+  </si>
+  <si>
+    <t>OM VELU NAIDU</t>
+  </si>
+  <si>
+    <t>PRATIK DILIP BORKAR</t>
+  </si>
+  <si>
+    <t>RAOUL TEOFILO DO ROSARIO VAS</t>
+  </si>
+  <si>
+    <t>REAIAH SHALOM FERNANDES</t>
+  </si>
+  <si>
+    <t>REEVE ALBERT RODRIGUES</t>
+  </si>
+  <si>
+    <t>REUBEN VALES</t>
+  </si>
+  <si>
+    <t>RHEA CLAIRE FERNANDES</t>
+  </si>
+  <si>
+    <t>RIDHIMA ROSHAN VERNEKAR</t>
+  </si>
+  <si>
+    <t>RIGEL SAMUEL FERNANDES</t>
+  </si>
+  <si>
+    <t>RIYA MARUTI KALAL</t>
+  </si>
+  <si>
+    <t>ROHIDAS MANIKRAO RAIKAR</t>
+  </si>
+  <si>
+    <t>RUCHA KASHINATH SAWANT</t>
+  </si>
+  <si>
+    <t>SALVA SAYAD</t>
+  </si>
+  <si>
+    <t>SANIL</t>
+  </si>
+  <si>
+    <t>SAUMYA VIKAS SHENVI MAUZEKAR</t>
+  </si>
+  <si>
+    <t>SHAWN STANTON DCOSTA</t>
+  </si>
+  <si>
+    <t>SHEEHAN RAPHAEL SA</t>
+  </si>
+  <si>
+    <t>SHIVAM CHOUHAN</t>
+  </si>
+  <si>
+    <t>SHOUNAK SURAJ VELIP</t>
+  </si>
+  <si>
+    <t>SHRAVANI RANJIT DHERE</t>
+  </si>
+  <si>
+    <t>SHREYA GOVIND JOSHI</t>
+  </si>
+  <si>
+    <t>SPARSH VISHAL ALVE</t>
+  </si>
+  <si>
+    <t>TABREJ ABUBAKKAR AGASNALI</t>
+  </si>
+  <si>
+    <t>TANISH SANJIV LOTLICAR</t>
+  </si>
+  <si>
+    <t>TROY</t>
+  </si>
+  <si>
+    <t>UTKARSHA UMESH TAKER</t>
+  </si>
+  <si>
+    <t>VANOSH CARL OZORIO FERNANDES</t>
+  </si>
+  <si>
+    <t>VANSHIKA GUPTA</t>
+  </si>
+  <si>
+    <t>VIHAAN VISHAL NAIK KARMALI</t>
+  </si>
+  <si>
+    <t>VRAJ ROSHAN POROB</t>
+  </si>
+  <si>
+    <t>YASH ANAND SURLEKAR</t>
   </si>
   <si>
     <t>ECS543</t>
@@ -412,34 +418,25 @@
     <t>FEB 2025</t>
   </si>
   <si>
-    <t>Digital Signal Processing</t>
-  </si>
-  <si>
-    <t>Testing &amp; Quality</t>
-  </si>
-  <si>
-    <t>Soft Computing 94</t>
+    <t>Digital Signal Processing Applications</t>
+  </si>
+  <si>
+    <t>Testing Quality Assurance</t>
+  </si>
+  <si>
+    <t>Soft Computing</t>
   </si>
   <si>
     <t>Database Systems Concepts</t>
   </si>
   <si>
-    <t>Soft Computing 40</t>
-  </si>
-  <si>
     <t>Ethics and Entrepreneurship</t>
   </si>
   <si>
-    <t>Transmission Lines &amp;</t>
-  </si>
-  <si>
-    <t>Occupational Safety and</t>
-  </si>
-  <si>
-    <t>Soft Computing 44</t>
-  </si>
-  <si>
-    <t>Soft Computing 63</t>
+    <t>Transmission Lines Antennas</t>
+  </si>
+  <si>
+    <t>Occupational Safety and Health</t>
   </si>
   <si>
     <t>Electronic Communication Systems</t>
@@ -448,299 +445,308 @@
     <t>Professional Elective Lab</t>
   </si>
   <si>
-    <t>Web-Technologies 69 P</t>
+    <t>Web-Technologies</t>
   </si>
   <si>
     <t>Database Systems Lab</t>
   </si>
   <si>
-    <t>Web-Technologies Soft Computing</t>
-  </si>
-  <si>
-    <t>60 P 13</t>
-  </si>
-  <si>
     <t>Soft Computing 74P</t>
   </si>
   <si>
-    <t>Soft Computing 56</t>
-  </si>
-  <si>
     <t>Control System Engineering</t>
   </si>
   <si>
-    <t>Fundamentals of Artificial</t>
-  </si>
-  <si>
-    <t>Soft Comiputing 40</t>
-  </si>
-  <si>
-    <t>Power Electronics 19</t>
-  </si>
-  <si>
-    <t>Web-Technologies 10 ECOMP533</t>
-  </si>
-  <si>
-    <t>Soff Computing 50</t>
-  </si>
-  <si>
-    <t>Soft Computing 46</t>
-  </si>
-  <si>
-    <t>ECOMP533 Web-Technologies Soft</t>
-  </si>
-  <si>
-    <t>Soft Computing 28</t>
-  </si>
-  <si>
-    <t>Power Electronics 40</t>
-  </si>
-  <si>
-    <t>Mechatronics 51 P</t>
-  </si>
-  <si>
-    <t>Soft Computing 21</t>
-  </si>
-  <si>
-    <t>Soft Computing 67</t>
-  </si>
-  <si>
-    <t>Mechatronics 77 P</t>
-  </si>
-  <si>
-    <t>Soft Computing 73</t>
-  </si>
-  <si>
-    <t>Mechatronics 65 P</t>
-  </si>
-  <si>
-    <t>Soft Computing 60</t>
+    <t>Fundamentals of Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>Soft Comiputing</t>
+  </si>
+  <si>
+    <t>Power Electronics</t>
+  </si>
+  <si>
+    <t>Soff Computing</t>
+  </si>
+  <si>
+    <t>Mechatronics</t>
+  </si>
+  <si>
+    <t>Digital Processing Applications</t>
   </si>
   <si>
     <t>Dalabase Systems Concepts</t>
   </si>
   <si>
-    <t>Mechatronics 36 F</t>
-  </si>
-  <si>
-    <t>Web-Technologies 71 P</t>
-  </si>
-  <si>
-    <t>Soft Computing 82</t>
-  </si>
-  <si>
     <t>Database Systems Iab</t>
   </si>
   <si>
-    <t>Soft Computing 45</t>
-  </si>
-  <si>
     <t>Electronic Communication Syslems</t>
   </si>
   <si>
-    <t>Soft Computing 41</t>
-  </si>
-  <si>
-    <t>Power Electronics 51</t>
-  </si>
-  <si>
     <t>Detabase Systems Concepts</t>
   </si>
   <si>
-    <t>Web-Technologies 74 P</t>
-  </si>
-  <si>
-    <t>Soft Computing 23</t>
-  </si>
-  <si>
-    <t>Power Electronics 66</t>
-  </si>
-  <si>
-    <t>Soft Computing 48</t>
-  </si>
-  <si>
-    <t>Soit Computing 78</t>
-  </si>
-  <si>
-    <t>Soft Computing 75</t>
-  </si>
-  <si>
-    <t>Soft Computing 53</t>
-  </si>
-  <si>
-    <t>57 P 12</t>
-  </si>
-  <si>
-    <t>Solt Computing 92</t>
-  </si>
-  <si>
-    <t>Mechatronics 97 P</t>
+    <t>Soit Computing</t>
+  </si>
+  <si>
+    <t>Solt Computing</t>
+  </si>
+  <si>
+    <t>Computing</t>
   </si>
   <si>
     <t>Professional Eleclive Lab</t>
   </si>
   <si>
-    <t>Soft Computing 58</t>
-  </si>
-  <si>
-    <t>Soft Computing 17</t>
-  </si>
-  <si>
-    <t>Soft Computing 77</t>
-  </si>
-  <si>
-    <t>Mechatronics 89 22</t>
-  </si>
-  <si>
-    <t>Soft Computing 76</t>
-  </si>
-  <si>
-    <t>Soft Computing 15</t>
-  </si>
-  <si>
-    <t>Power Electronics 11</t>
-  </si>
-  <si>
-    <t>Mechatronics 15 F</t>
-  </si>
-  <si>
-    <t>Soft Cornputing 50</t>
-  </si>
-  <si>
-    <t>Soft Computing 25</t>
-  </si>
-  <si>
-    <t>Soft Computing 43</t>
+    <t>Soft Cornputing</t>
   </si>
   <si>
     <t>Database Systers Concepts</t>
   </si>
   <si>
-    <t>Web-Technologies 62 P</t>
-  </si>
-  <si>
-    <t>Soft Computing 51</t>
-  </si>
-  <si>
-    <t>Soft Computing 27</t>
-  </si>
-  <si>
-    <t>Mechatronics 21 F</t>
-  </si>
-  <si>
     <t>Database Syslems Concepts</t>
   </si>
   <si>
-    <t>Soft Computing 47</t>
-  </si>
-  <si>
-    <t>Soft Computing 55</t>
-  </si>
-  <si>
-    <t>Web-Technologies 83 P</t>
-  </si>
-  <si>
-    <t>Soft Computing 78</t>
-  </si>
-  <si>
-    <t>Fundamentals of Aitificial</t>
-  </si>
-  <si>
-    <t>Web-Technologies 74 21</t>
-  </si>
-  <si>
-    <t>Soft Computing 68</t>
-  </si>
-  <si>
-    <t>Soft Computing 54</t>
-  </si>
-  <si>
-    <t>Asstt: Registre Exam(Prof)</t>
+    <t>Fundamentals of Aitificial Intelligence</t>
+  </si>
+  <si>
+    <t>Asstt: Registre Exam(Prof) Asstt. Registrar Exam</t>
   </si>
   <si>
     <t>P</t>
   </si>
   <si>
+    <t>B+</t>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
     <t>F</t>
   </si>
   <si>
-    <t>B+</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>83</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -803,13 +809,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -847,7 +861,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -881,6 +895,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -915,9 +930,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1090,11 +1106,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F268"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="57.33203125" customWidth="1"/>
+    <col min="3" max="3" width="32.77734375" customWidth="1"/>
+    <col min="4" max="4" width="37.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1114,7 +1135,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1128,13 +1149,13 @@
         <v>132</v>
       </c>
       <c r="E2" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1148,13 +1169,13 @@
         <v>133</v>
       </c>
       <c r="E3" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F3" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1168,13 +1189,13 @@
         <v>134</v>
       </c>
       <c r="E4" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F4" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1188,13 +1209,13 @@
         <v>135</v>
       </c>
       <c r="E5" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="F5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1208,13 +1229,13 @@
         <v>132</v>
       </c>
       <c r="E6" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F6" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1228,13 +1249,13 @@
         <v>133</v>
       </c>
       <c r="E7" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F7" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1245,16 +1266,16 @@
         <v>118</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E8" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F8" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1265,16 +1286,16 @@
         <v>120</v>
       </c>
       <c r="D9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E9" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F9" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1288,13 +1309,13 @@
         <v>135</v>
       </c>
       <c r="E10" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F10" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -1305,16 +1326,16 @@
         <v>121</v>
       </c>
       <c r="D11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E11" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F11" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -1325,16 +1346,16 @@
         <v>122</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E12" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F12" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -1345,16 +1366,16 @@
         <v>118</v>
       </c>
       <c r="D13" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E13" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F13" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1368,13 +1389,13 @@
         <v>132</v>
       </c>
       <c r="E14" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F14" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -1388,13 +1409,13 @@
         <v>133</v>
       </c>
       <c r="E15" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F15" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -1405,16 +1426,16 @@
         <v>118</v>
       </c>
       <c r="D16" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E16" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F16" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -1425,16 +1446,16 @@
         <v>123</v>
       </c>
       <c r="D17" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E17" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="F17" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -1448,13 +1469,13 @@
         <v>135</v>
       </c>
       <c r="E18" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="F18" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -1465,16 +1486,16 @@
         <v>121</v>
       </c>
       <c r="D19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E19" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F19" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1485,16 +1506,16 @@
         <v>124</v>
       </c>
       <c r="D20" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E20" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F20" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -1505,16 +1526,16 @@
         <v>125</v>
       </c>
       <c r="D21" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E21" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F21" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -1525,16 +1546,16 @@
         <v>118</v>
       </c>
       <c r="D22" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E22" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F22" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -1548,13 +1569,13 @@
         <v>135</v>
       </c>
       <c r="E23" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F23" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -1568,13 +1589,13 @@
         <v>132</v>
       </c>
       <c r="E24" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -1585,16 +1606,16 @@
         <v>126</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E25" t="s">
-        <v>216</v>
+        <v>164</v>
       </c>
       <c r="F25" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -1605,16 +1626,16 @@
         <v>125</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E26" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F26" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -1625,16 +1646,16 @@
         <v>118</v>
       </c>
       <c r="D27" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E27" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F27" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -1648,13 +1669,13 @@
         <v>135</v>
       </c>
       <c r="E28" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F28" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -1668,13 +1689,13 @@
         <v>132</v>
       </c>
       <c r="E29" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F29" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -1688,13 +1709,13 @@
         <v>133</v>
       </c>
       <c r="E30" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F30" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -1705,16 +1726,16 @@
         <v>118</v>
       </c>
       <c r="D31" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E31" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F31" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>13</v>
       </c>
@@ -1728,13 +1749,13 @@
         <v>135</v>
       </c>
       <c r="E32" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F32" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>13</v>
       </c>
@@ -1745,16 +1766,16 @@
         <v>126</v>
       </c>
       <c r="D33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E33" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F33" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>13</v>
       </c>
@@ -1765,16 +1786,16 @@
         <v>124</v>
       </c>
       <c r="D34" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E34" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F34" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>13</v>
       </c>
@@ -1788,13 +1809,13 @@
         <v>133</v>
       </c>
       <c r="E35" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F35" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>13</v>
       </c>
@@ -1805,16 +1826,16 @@
         <v>118</v>
       </c>
       <c r="D36" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="E36" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F36" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -1825,16 +1846,16 @@
         <v>127</v>
       </c>
       <c r="D37" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E37" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F37" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -1848,13 +1869,13 @@
         <v>135</v>
       </c>
       <c r="E38" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F38" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -1868,13 +1889,13 @@
         <v>132</v>
       </c>
       <c r="E39" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F39" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>14</v>
       </c>
@@ -1888,13 +1909,13 @@
         <v>133</v>
       </c>
       <c r="E40" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F40" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>14</v>
       </c>
@@ -1905,16 +1926,16 @@
         <v>118</v>
       </c>
       <c r="D41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E41" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F41" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>14</v>
       </c>
@@ -1925,16 +1946,16 @@
         <v>128</v>
       </c>
       <c r="D42" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E42" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F42" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>15</v>
       </c>
@@ -1948,13 +1969,13 @@
         <v>135</v>
       </c>
       <c r="E43" t="s">
-        <v>215</v>
+        <v>167</v>
       </c>
       <c r="F43" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -1965,16 +1986,16 @@
         <v>121</v>
       </c>
       <c r="D44" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E44" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F44" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -1985,16 +2006,16 @@
         <v>124</v>
       </c>
       <c r="D45" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E45" t="s">
-        <v>215</v>
+        <v>167</v>
       </c>
       <c r="F45" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>15</v>
       </c>
@@ -2005,16 +2026,16 @@
         <v>122</v>
       </c>
       <c r="D46" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E46" t="s">
-        <v>215</v>
+        <v>167</v>
       </c>
       <c r="F46" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>15</v>
       </c>
@@ -2025,16 +2046,16 @@
         <v>118</v>
       </c>
       <c r="D47" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E47" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="F47" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>16</v>
       </c>
@@ -2045,16 +2066,16 @@
         <v>123</v>
       </c>
       <c r="D48" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E48" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F48" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>16</v>
       </c>
@@ -2065,16 +2086,16 @@
         <v>126</v>
       </c>
       <c r="D49" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E49" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="F49" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>16</v>
       </c>
@@ -2088,13 +2109,13 @@
         <v>133</v>
       </c>
       <c r="E50" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F50" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>16</v>
       </c>
@@ -2105,16 +2126,16 @@
         <v>118</v>
       </c>
       <c r="D51" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E51" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F51" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>16</v>
       </c>
@@ -2125,16 +2146,16 @@
         <v>129</v>
       </c>
       <c r="D52" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E52" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="F52" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>17</v>
       </c>
@@ -2148,13 +2169,13 @@
         <v>132</v>
       </c>
       <c r="E53" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F53" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -2165,16 +2186,16 @@
         <v>124</v>
       </c>
       <c r="D54" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E54" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F54" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>17</v>
       </c>
@@ -2185,16 +2206,16 @@
         <v>125</v>
       </c>
       <c r="D55" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E55" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F55" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -2205,16 +2226,16 @@
         <v>118</v>
       </c>
       <c r="D56" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E56" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F56" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -2225,16 +2246,16 @@
         <v>128</v>
       </c>
       <c r="D57" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E57" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F57" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -2245,16 +2266,16 @@
         <v>123</v>
       </c>
       <c r="D58" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E58" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F58" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -2268,13 +2289,13 @@
         <v>135</v>
       </c>
       <c r="E59" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F59" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -2288,13 +2309,13 @@
         <v>132</v>
       </c>
       <c r="E60" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F60" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -2305,16 +2326,16 @@
         <v>124</v>
       </c>
       <c r="D61" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E61" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F61" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -2328,13 +2349,13 @@
         <v>133</v>
       </c>
       <c r="E62" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F62" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -2345,16 +2366,16 @@
         <v>118</v>
       </c>
       <c r="D63" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="E63" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F63" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -2365,16 +2386,16 @@
         <v>128</v>
       </c>
       <c r="D64" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E64" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F64" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>19</v>
       </c>
@@ -2388,13 +2409,13 @@
         <v>132</v>
       </c>
       <c r="E65" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F65" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>19</v>
       </c>
@@ -2405,16 +2426,16 @@
         <v>125</v>
       </c>
       <c r="D66" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="E66" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F66" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>19</v>
       </c>
@@ -2425,16 +2446,16 @@
         <v>118</v>
       </c>
       <c r="D67" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E67" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F67" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>20</v>
       </c>
@@ -2445,16 +2466,16 @@
         <v>124</v>
       </c>
       <c r="D68" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E68" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="F68" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>20</v>
       </c>
@@ -2465,16 +2486,16 @@
         <v>118</v>
       </c>
       <c r="D69" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="E69" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="F69" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>20</v>
       </c>
@@ -2485,16 +2506,16 @@
         <v>129</v>
       </c>
       <c r="D70" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="E70" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F70" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>20</v>
       </c>
@@ -2505,16 +2526,16 @@
         <v>130</v>
       </c>
       <c r="D71" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="E71" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F71" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>21</v>
       </c>
@@ -2528,13 +2549,13 @@
         <v>135</v>
       </c>
       <c r="E72" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="F72" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>21</v>
       </c>
@@ -2545,16 +2566,16 @@
         <v>121</v>
       </c>
       <c r="D73" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E73" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F73" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>21</v>
       </c>
@@ -2565,16 +2586,16 @@
         <v>122</v>
       </c>
       <c r="D74" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E74" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F74" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>21</v>
       </c>
@@ -2585,16 +2606,16 @@
         <v>118</v>
       </c>
       <c r="D75" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E75" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F75" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>22</v>
       </c>
@@ -2608,13 +2629,13 @@
         <v>135</v>
       </c>
       <c r="E76" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="F76" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>22</v>
       </c>
@@ -2628,13 +2649,13 @@
         <v>133</v>
       </c>
       <c r="E77" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="F77" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>22</v>
       </c>
@@ -2645,16 +2666,16 @@
         <v>118</v>
       </c>
       <c r="D78" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="E78" t="s">
-        <v>215</v>
+        <v>167</v>
       </c>
       <c r="F78" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>22</v>
       </c>
@@ -2665,16 +2686,16 @@
         <v>127</v>
       </c>
       <c r="D79" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E79" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="F79" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>23</v>
       </c>
@@ -2688,13 +2709,13 @@
         <v>135</v>
       </c>
       <c r="E80" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F80" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>23</v>
       </c>
@@ -2705,16 +2726,16 @@
         <v>118</v>
       </c>
       <c r="D81" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="E81" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F81" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>23</v>
       </c>
@@ -2725,16 +2746,16 @@
         <v>127</v>
       </c>
       <c r="D82" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E82" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F82" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>23</v>
       </c>
@@ -2745,16 +2766,16 @@
         <v>130</v>
       </c>
       <c r="D83" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="E83" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F83" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>23</v>
       </c>
@@ -2765,16 +2786,16 @@
         <v>128</v>
       </c>
       <c r="D84" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E84" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F84" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>24</v>
       </c>
@@ -2788,13 +2809,13 @@
         <v>135</v>
       </c>
       <c r="E85" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F85" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>24</v>
       </c>
@@ -2808,13 +2829,13 @@
         <v>132</v>
       </c>
       <c r="E86" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F86" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>24</v>
       </c>
@@ -2825,16 +2846,16 @@
         <v>126</v>
       </c>
       <c r="D87" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E87" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F87" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>24</v>
       </c>
@@ -2845,16 +2866,16 @@
         <v>118</v>
       </c>
       <c r="D88" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="E88" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F88" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>24</v>
       </c>
@@ -2865,16 +2886,16 @@
         <v>130</v>
       </c>
       <c r="D89" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="E89" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F89" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>25</v>
       </c>
@@ -2885,16 +2906,16 @@
         <v>123</v>
       </c>
       <c r="D90" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E90" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="F90" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>25</v>
       </c>
@@ -2908,13 +2929,13 @@
         <v>135</v>
       </c>
       <c r="E91" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F91" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>25</v>
       </c>
@@ -2925,16 +2946,16 @@
         <v>116</v>
       </c>
       <c r="D92" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="E92" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F92" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>25</v>
       </c>
@@ -2945,16 +2966,16 @@
         <v>126</v>
       </c>
       <c r="D93" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E93" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F93" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>25</v>
       </c>
@@ -2965,16 +2986,16 @@
         <v>124</v>
       </c>
       <c r="D94" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E94" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F94" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>25</v>
       </c>
@@ -2988,13 +3009,13 @@
         <v>133</v>
       </c>
       <c r="E95" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F95" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>25</v>
       </c>
@@ -3005,16 +3026,16 @@
         <v>118</v>
       </c>
       <c r="D96" t="s">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="E96" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F96" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>26</v>
       </c>
@@ -3025,16 +3046,16 @@
         <v>123</v>
       </c>
       <c r="D97" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E97" t="s">
-        <v>215</v>
+        <v>167</v>
       </c>
       <c r="F97" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>26</v>
       </c>
@@ -3045,16 +3066,16 @@
         <v>119</v>
       </c>
       <c r="D98" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="E98" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F98" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>26</v>
       </c>
@@ -3065,16 +3086,16 @@
         <v>126</v>
       </c>
       <c r="D99" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E99" t="s">
+        <v>164</v>
+      </c>
+      <c r="F99" t="s">
         <v>214</v>
       </c>
-      <c r="F99" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>26</v>
       </c>
@@ -3085,16 +3106,16 @@
         <v>118</v>
       </c>
       <c r="D100" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E100" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="F100" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>26</v>
       </c>
@@ -3105,16 +3126,16 @@
         <v>127</v>
       </c>
       <c r="D101" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E101" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="F101" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>26</v>
       </c>
@@ -3125,16 +3146,16 @@
         <v>120</v>
       </c>
       <c r="D102" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E102" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="F102" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>26</v>
       </c>
@@ -3145,16 +3166,16 @@
         <v>130</v>
       </c>
       <c r="D103" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="E103" t="s">
+        <v>167</v>
+      </c>
+      <c r="F103" t="s">
         <v>215</v>
       </c>
-      <c r="F103" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>27</v>
       </c>
@@ -3168,13 +3189,13 @@
         <v>135</v>
       </c>
       <c r="E104" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F104" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>27</v>
       </c>
@@ -3188,13 +3209,13 @@
         <v>132</v>
       </c>
       <c r="E105" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F105" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>27</v>
       </c>
@@ -3205,16 +3226,16 @@
         <v>126</v>
       </c>
       <c r="D106" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E106" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F106" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>27</v>
       </c>
@@ -3225,16 +3246,16 @@
         <v>125</v>
       </c>
       <c r="D107" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="E107" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F107" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>27</v>
       </c>
@@ -3245,16 +3266,16 @@
         <v>118</v>
       </c>
       <c r="D108" t="s">
-        <v>170</v>
+        <v>134</v>
       </c>
       <c r="E108" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F108" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>28</v>
       </c>
@@ -3268,13 +3289,13 @@
         <v>135</v>
       </c>
       <c r="E109" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F109" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>28</v>
       </c>
@@ -3285,16 +3306,16 @@
         <v>121</v>
       </c>
       <c r="D110" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E110" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F110" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>28</v>
       </c>
@@ -3305,16 +3326,16 @@
         <v>126</v>
       </c>
       <c r="D111" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="E111" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F111" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>28</v>
       </c>
@@ -3325,16 +3346,16 @@
         <v>122</v>
       </c>
       <c r="D112" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E112" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F112" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>28</v>
       </c>
@@ -3345,16 +3366,16 @@
         <v>118</v>
       </c>
       <c r="D113" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="E113" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F113" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>29</v>
       </c>
@@ -3365,16 +3386,16 @@
         <v>123</v>
       </c>
       <c r="D114" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="E114" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="F114" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>29</v>
       </c>
@@ -3385,16 +3406,16 @@
         <v>122</v>
       </c>
       <c r="D115" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E115" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F115" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>29</v>
       </c>
@@ -3405,16 +3426,16 @@
         <v>118</v>
       </c>
       <c r="D116" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="E116" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F116" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>29</v>
       </c>
@@ -3425,16 +3446,16 @@
         <v>129</v>
       </c>
       <c r="D117" t="s">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="E117" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F117" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>30</v>
       </c>
@@ -3445,16 +3466,16 @@
         <v>119</v>
       </c>
       <c r="D118" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="E118" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="F118" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>30</v>
       </c>
@@ -3465,16 +3486,16 @@
         <v>126</v>
       </c>
       <c r="D119" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E119" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F119" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>30</v>
       </c>
@@ -3485,16 +3506,16 @@
         <v>125</v>
       </c>
       <c r="D120" t="s">
-        <v>177</v>
+        <v>141</v>
       </c>
       <c r="E120" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F120" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>30</v>
       </c>
@@ -3505,16 +3526,16 @@
         <v>118</v>
       </c>
       <c r="D121" t="s">
-        <v>178</v>
+        <v>134</v>
       </c>
       <c r="E121" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="F121" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>30</v>
       </c>
@@ -3525,16 +3546,16 @@
         <v>129</v>
       </c>
       <c r="D122" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="E122" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F122" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>31</v>
       </c>
@@ -3548,13 +3569,13 @@
         <v>135</v>
       </c>
       <c r="E123" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F123" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>31</v>
       </c>
@@ -3565,16 +3586,16 @@
         <v>122</v>
       </c>
       <c r="D124" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E124" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F124" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>31</v>
       </c>
@@ -3585,16 +3606,16 @@
         <v>118</v>
       </c>
       <c r="D125" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="E125" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F125" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>31</v>
       </c>
@@ -3605,16 +3626,16 @@
         <v>129</v>
       </c>
       <c r="D126" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="E126" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F126" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>32</v>
       </c>
@@ -3628,13 +3649,13 @@
         <v>135</v>
       </c>
       <c r="E127" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F127" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>32</v>
       </c>
@@ -3648,13 +3669,13 @@
         <v>132</v>
       </c>
       <c r="E128" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F128" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>32</v>
       </c>
@@ -3668,13 +3689,13 @@
         <v>133</v>
       </c>
       <c r="E129" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F129" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>32</v>
       </c>
@@ -3685,16 +3706,16 @@
         <v>118</v>
       </c>
       <c r="D130" t="s">
-        <v>180</v>
+        <v>134</v>
       </c>
       <c r="E130" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F130" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>32</v>
       </c>
@@ -3705,16 +3726,16 @@
         <v>128</v>
       </c>
       <c r="D131" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E131" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F131" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>33</v>
       </c>
@@ -3728,13 +3749,13 @@
         <v>132</v>
       </c>
       <c r="E132" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F132" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>33</v>
       </c>
@@ -3748,13 +3769,13 @@
         <v>133</v>
       </c>
       <c r="E133" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F133" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>33</v>
       </c>
@@ -3765,16 +3786,16 @@
         <v>118</v>
       </c>
       <c r="D134" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="E134" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F134" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>33</v>
       </c>
@@ -3785,16 +3806,16 @@
         <v>128</v>
       </c>
       <c r="D135" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E135" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F135" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>34</v>
       </c>
@@ -3808,13 +3829,13 @@
         <v>132</v>
       </c>
       <c r="E136" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F136" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>34</v>
       </c>
@@ -3828,13 +3849,13 @@
         <v>133</v>
       </c>
       <c r="E137" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F137" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>34</v>
       </c>
@@ -3845,16 +3866,16 @@
         <v>118</v>
       </c>
       <c r="D138" t="s">
-        <v>182</v>
+        <v>134</v>
       </c>
       <c r="E138" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F138" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>34</v>
       </c>
@@ -3865,16 +3886,16 @@
         <v>128</v>
       </c>
       <c r="D139" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E139" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F139" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>35</v>
       </c>
@@ -3885,16 +3906,16 @@
         <v>121</v>
       </c>
       <c r="D140" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E140" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F140" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>35</v>
       </c>
@@ -3905,16 +3926,16 @@
         <v>126</v>
       </c>
       <c r="D141" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E141" t="s">
+        <v>164</v>
+      </c>
+      <c r="F141" t="s">
         <v>214</v>
       </c>
-      <c r="F141" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>35</v>
       </c>
@@ -3925,16 +3946,16 @@
         <v>122</v>
       </c>
       <c r="D142" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E142" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F142" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>35</v>
       </c>
@@ -3945,16 +3966,16 @@
         <v>118</v>
       </c>
       <c r="D143" t="s">
-        <v>183</v>
+        <v>134</v>
       </c>
       <c r="E143" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F143" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>36</v>
       </c>
@@ -3965,16 +3986,16 @@
         <v>119</v>
       </c>
       <c r="D144" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="E144" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F144" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>36</v>
       </c>
@@ -3985,16 +4006,16 @@
         <v>121</v>
       </c>
       <c r="D145" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E145" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F145" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>36</v>
       </c>
@@ -4005,16 +4026,16 @@
         <v>124</v>
       </c>
       <c r="D146" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E146" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F146" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>36</v>
       </c>
@@ -4028,13 +4049,13 @@
         <v>133</v>
       </c>
       <c r="E147" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F147" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>36</v>
       </c>
@@ -4045,16 +4066,16 @@
         <v>118</v>
       </c>
       <c r="D148" t="s">
-        <v>184</v>
+        <v>134</v>
       </c>
       <c r="E148" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F148" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>37</v>
       </c>
@@ -4068,13 +4089,13 @@
         <v>135</v>
       </c>
       <c r="E149" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F149" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>37</v>
       </c>
@@ -4085,16 +4106,16 @@
         <v>126</v>
       </c>
       <c r="D150" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E150" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F150" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>37</v>
       </c>
@@ -4105,16 +4126,16 @@
         <v>124</v>
       </c>
       <c r="D151" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E151" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F151" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>37</v>
       </c>
@@ -4125,16 +4146,16 @@
         <v>118</v>
       </c>
       <c r="D152" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="E152" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F152" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>37</v>
       </c>
@@ -4145,16 +4166,16 @@
         <v>127</v>
       </c>
       <c r="D153" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E153" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F153" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>37</v>
       </c>
@@ -4165,16 +4186,16 @@
         <v>130</v>
       </c>
       <c r="D154" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
       <c r="E154" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F154" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>38</v>
       </c>
@@ -4188,13 +4209,13 @@
         <v>135</v>
       </c>
       <c r="E155" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F155" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>38</v>
       </c>
@@ -4205,16 +4226,16 @@
         <v>121</v>
       </c>
       <c r="D156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E156" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F156" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>38</v>
       </c>
@@ -4225,16 +4246,16 @@
         <v>122</v>
       </c>
       <c r="D157" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E157" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F157" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>38</v>
       </c>
@@ -4245,16 +4266,16 @@
         <v>118</v>
       </c>
       <c r="D158" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="E158" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F158" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>39</v>
       </c>
@@ -4268,13 +4289,13 @@
         <v>135</v>
       </c>
       <c r="E159" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F159" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>39</v>
       </c>
@@ -4288,13 +4309,13 @@
         <v>132</v>
       </c>
       <c r="E160" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F160" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>39</v>
       </c>
@@ -4305,16 +4326,16 @@
         <v>124</v>
       </c>
       <c r="D161" t="s">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="E161" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F161" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>39</v>
       </c>
@@ -4328,13 +4349,13 @@
         <v>133</v>
       </c>
       <c r="E162" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F162" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>39</v>
       </c>
@@ -4345,16 +4366,16 @@
         <v>118</v>
       </c>
       <c r="D163" t="s">
-        <v>188</v>
+        <v>134</v>
       </c>
       <c r="E163" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F163" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>39</v>
       </c>
@@ -4365,16 +4386,16 @@
         <v>128</v>
       </c>
       <c r="D164" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E164" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F164" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>40</v>
       </c>
@@ -4388,13 +4409,13 @@
         <v>132</v>
       </c>
       <c r="E165" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="F165" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>40</v>
       </c>
@@ -4405,16 +4426,16 @@
         <v>124</v>
       </c>
       <c r="D166" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E166" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="F166" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>40</v>
       </c>
@@ -4428,13 +4449,13 @@
         <v>133</v>
       </c>
       <c r="E167" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="F167" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>40</v>
       </c>
@@ -4445,16 +4466,16 @@
         <v>118</v>
       </c>
       <c r="D168" t="s">
-        <v>189</v>
+        <v>134</v>
       </c>
       <c r="E168" t="s">
-        <v>215</v>
+        <v>167</v>
       </c>
       <c r="F168" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>41</v>
       </c>
@@ -4465,16 +4486,16 @@
         <v>118</v>
       </c>
       <c r="D169" t="s">
-        <v>190</v>
+        <v>134</v>
       </c>
       <c r="E169" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F169" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>41</v>
       </c>
@@ -4485,16 +4506,16 @@
         <v>127</v>
       </c>
       <c r="D170" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E170" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F170" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>41</v>
       </c>
@@ -4505,16 +4526,16 @@
         <v>130</v>
       </c>
       <c r="D171" t="s">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="E171" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F171" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>41</v>
       </c>
@@ -4525,16 +4546,16 @@
         <v>128</v>
       </c>
       <c r="D172" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E172" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F172" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>42</v>
       </c>
@@ -4548,13 +4569,13 @@
         <v>135</v>
       </c>
       <c r="E173" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F173" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>42</v>
       </c>
@@ -4568,13 +4589,13 @@
         <v>132</v>
       </c>
       <c r="E174" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F174" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>42</v>
       </c>
@@ -4588,13 +4609,13 @@
         <v>133</v>
       </c>
       <c r="E175" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F175" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>42</v>
       </c>
@@ -4605,16 +4626,16 @@
         <v>118</v>
       </c>
       <c r="D176" t="s">
+        <v>134</v>
+      </c>
+      <c r="E176" t="s">
+        <v>165</v>
+      </c>
+      <c r="F176" t="s">
         <v>174</v>
       </c>
-      <c r="E176" t="s">
-        <v>214</v>
-      </c>
-      <c r="F176" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6">
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>43</v>
       </c>
@@ -4628,13 +4649,13 @@
         <v>135</v>
       </c>
       <c r="E177" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="F177" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>43</v>
       </c>
@@ -4648,13 +4669,13 @@
         <v>132</v>
       </c>
       <c r="E178" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="F178" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>43</v>
       </c>
@@ -4665,16 +4686,16 @@
         <v>126</v>
       </c>
       <c r="D179" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E179" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F179" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>43</v>
       </c>
@@ -4685,16 +4706,16 @@
         <v>124</v>
       </c>
       <c r="D180" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E180" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F180" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>43</v>
       </c>
@@ -4708,13 +4729,13 @@
         <v>133</v>
       </c>
       <c r="E181" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F181" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>43</v>
       </c>
@@ -4725,16 +4746,16 @@
         <v>118</v>
       </c>
       <c r="D182" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E182" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F182" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>44</v>
       </c>
@@ -4748,13 +4769,13 @@
         <v>132</v>
       </c>
       <c r="E183" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F183" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>44</v>
       </c>
@@ -4765,16 +4786,16 @@
         <v>126</v>
       </c>
       <c r="D184" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E184" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F184" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>44</v>
       </c>
@@ -4785,16 +4806,16 @@
         <v>124</v>
       </c>
       <c r="D185" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E185" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F185" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>44</v>
       </c>
@@ -4808,13 +4829,13 @@
         <v>133</v>
       </c>
       <c r="E186" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F186" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>44</v>
       </c>
@@ -4825,16 +4846,16 @@
         <v>118</v>
       </c>
       <c r="D187" t="s">
-        <v>192</v>
+        <v>134</v>
       </c>
       <c r="E187" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F187" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>45</v>
       </c>
@@ -4848,13 +4869,13 @@
         <v>135</v>
       </c>
       <c r="E188" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F188" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>45</v>
       </c>
@@ -4865,16 +4886,16 @@
         <v>121</v>
       </c>
       <c r="D189" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E189" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F189" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>45</v>
       </c>
@@ -4885,16 +4906,16 @@
         <v>126</v>
       </c>
       <c r="D190" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E190" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F190" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>45</v>
       </c>
@@ -4905,16 +4926,16 @@
         <v>124</v>
       </c>
       <c r="D191" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E191" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F191" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>45</v>
       </c>
@@ -4928,13 +4949,13 @@
         <v>133</v>
       </c>
       <c r="E192" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F192" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>45</v>
       </c>
@@ -4945,16 +4966,16 @@
         <v>118</v>
       </c>
       <c r="D193" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E193" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F193" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>46</v>
       </c>
@@ -4968,13 +4989,13 @@
         <v>135</v>
       </c>
       <c r="E194" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="F194" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>46</v>
       </c>
@@ -4985,16 +5006,16 @@
         <v>118</v>
       </c>
       <c r="D195" t="s">
-        <v>193</v>
+        <v>134</v>
       </c>
       <c r="E195" t="s">
-        <v>215</v>
+        <v>167</v>
       </c>
       <c r="F195" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>46</v>
       </c>
@@ -5005,16 +5026,16 @@
         <v>129</v>
       </c>
       <c r="D196" t="s">
-        <v>194</v>
+        <v>147</v>
       </c>
       <c r="E196" t="s">
-        <v>215</v>
+        <v>167</v>
       </c>
       <c r="F196" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>46</v>
       </c>
@@ -5025,16 +5046,16 @@
         <v>130</v>
       </c>
       <c r="D197" t="s">
-        <v>195</v>
+        <v>149</v>
       </c>
       <c r="E197" t="s">
-        <v>215</v>
+        <v>167</v>
       </c>
       <c r="F197" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>47</v>
       </c>
@@ -5048,13 +5069,13 @@
         <v>135</v>
       </c>
       <c r="E198" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F198" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>47</v>
       </c>
@@ -5068,13 +5089,13 @@
         <v>132</v>
       </c>
       <c r="E199" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F199" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>47</v>
       </c>
@@ -5088,13 +5109,13 @@
         <v>133</v>
       </c>
       <c r="E200" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F200" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>47</v>
       </c>
@@ -5105,16 +5126,16 @@
         <v>118</v>
       </c>
       <c r="D201" t="s">
-        <v>196</v>
+        <v>159</v>
       </c>
       <c r="E201" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F201" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>48</v>
       </c>
@@ -5125,16 +5146,16 @@
         <v>118</v>
       </c>
       <c r="D202" t="s">
-        <v>197</v>
+        <v>134</v>
       </c>
       <c r="E202" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="F202" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>48</v>
       </c>
@@ -5145,16 +5166,16 @@
         <v>127</v>
       </c>
       <c r="D203" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E203" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F203" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>48</v>
       </c>
@@ -5165,16 +5186,16 @@
         <v>120</v>
       </c>
       <c r="D204" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E204" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F204" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>48</v>
       </c>
@@ -5185,16 +5206,16 @@
         <v>130</v>
       </c>
       <c r="D205" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="E205" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F205" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>49</v>
       </c>
@@ -5205,16 +5226,16 @@
         <v>126</v>
       </c>
       <c r="D206" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E206" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F206" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>49</v>
       </c>
@@ -5228,13 +5249,13 @@
         <v>133</v>
       </c>
       <c r="E207" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F207" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>49</v>
       </c>
@@ -5245,16 +5266,16 @@
         <v>118</v>
       </c>
       <c r="D208" t="s">
-        <v>198</v>
+        <v>134</v>
       </c>
       <c r="E208" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F208" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>49</v>
       </c>
@@ -5265,16 +5286,16 @@
         <v>127</v>
       </c>
       <c r="D209" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E209" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F209" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>50</v>
       </c>
@@ -5285,16 +5306,16 @@
         <v>119</v>
       </c>
       <c r="D210" t="s">
-        <v>199</v>
+        <v>160</v>
       </c>
       <c r="E210" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F210" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>50</v>
       </c>
@@ -5305,16 +5326,16 @@
         <v>121</v>
       </c>
       <c r="D211" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E211" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="F211" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>50</v>
       </c>
@@ -5325,16 +5346,16 @@
         <v>126</v>
       </c>
       <c r="D212" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E212" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F212" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>50</v>
       </c>
@@ -5345,16 +5366,16 @@
         <v>124</v>
       </c>
       <c r="D213" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E213" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F213" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>50</v>
       </c>
@@ -5365,16 +5386,16 @@
         <v>125</v>
       </c>
       <c r="D214" t="s">
-        <v>200</v>
+        <v>141</v>
       </c>
       <c r="E214" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F214" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>50</v>
       </c>
@@ -5385,16 +5406,16 @@
         <v>118</v>
       </c>
       <c r="D215" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="E215" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="F215" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>51</v>
       </c>
@@ -5408,13 +5429,13 @@
         <v>135</v>
       </c>
       <c r="E216" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F216" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>51</v>
       </c>
@@ -5428,13 +5449,13 @@
         <v>132</v>
       </c>
       <c r="E217" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F217" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>51</v>
       </c>
@@ -5445,16 +5466,16 @@
         <v>126</v>
       </c>
       <c r="D218" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E218" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F218" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>51</v>
       </c>
@@ -5468,13 +5489,13 @@
         <v>133</v>
       </c>
       <c r="E219" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F219" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>51</v>
       </c>
@@ -5485,16 +5506,16 @@
         <v>118</v>
       </c>
       <c r="D220" t="s">
-        <v>201</v>
+        <v>134</v>
       </c>
       <c r="E220" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F220" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>52</v>
       </c>
@@ -5508,13 +5529,13 @@
         <v>135</v>
       </c>
       <c r="E221" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F221" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>52</v>
       </c>
@@ -5528,13 +5549,13 @@
         <v>132</v>
       </c>
       <c r="E222" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F222" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>52</v>
       </c>
@@ -5545,16 +5566,16 @@
         <v>126</v>
       </c>
       <c r="D223" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E223" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F223" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>52</v>
       </c>
@@ -5565,16 +5586,16 @@
         <v>124</v>
       </c>
       <c r="D224" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E224" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F224" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>52</v>
       </c>
@@ -5588,13 +5609,13 @@
         <v>133</v>
       </c>
       <c r="E225" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F225" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>52</v>
       </c>
@@ -5605,16 +5626,16 @@
         <v>118</v>
       </c>
       <c r="D226" t="s">
-        <v>170</v>
+        <v>134</v>
       </c>
       <c r="E226" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F226" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>52</v>
       </c>
@@ -5625,16 +5646,16 @@
         <v>120</v>
       </c>
       <c r="D227" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E227" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F227" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>53</v>
       </c>
@@ -5645,16 +5666,16 @@
         <v>123</v>
       </c>
       <c r="D228" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E228" t="s">
-        <v>215</v>
+        <v>167</v>
       </c>
       <c r="F228" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="229" spans="1:6">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>53</v>
       </c>
@@ -5668,13 +5689,13 @@
         <v>135</v>
       </c>
       <c r="E229" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F229" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>53</v>
       </c>
@@ -5685,16 +5706,16 @@
         <v>124</v>
       </c>
       <c r="D230" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E230" t="s">
-        <v>215</v>
+        <v>167</v>
       </c>
       <c r="F230" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>53</v>
       </c>
@@ -5705,16 +5726,16 @@
         <v>118</v>
       </c>
       <c r="D231" t="s">
-        <v>202</v>
+        <v>134</v>
       </c>
       <c r="E231" t="s">
-        <v>215</v>
+        <v>167</v>
       </c>
       <c r="F231" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="232" spans="1:6">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>53</v>
       </c>
@@ -5725,16 +5746,16 @@
         <v>129</v>
       </c>
       <c r="D232" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="E232" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="F232" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>53</v>
       </c>
@@ -5745,16 +5766,16 @@
         <v>130</v>
       </c>
       <c r="D233" t="s">
-        <v>203</v>
+        <v>149</v>
       </c>
       <c r="E233" t="s">
-        <v>215</v>
+        <v>167</v>
       </c>
       <c r="F233" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>54</v>
       </c>
@@ -5765,16 +5786,16 @@
         <v>119</v>
       </c>
       <c r="D234" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="E234" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="F234" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>54</v>
       </c>
@@ -5785,16 +5806,16 @@
         <v>121</v>
       </c>
       <c r="D235" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E235" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="F235" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>54</v>
       </c>
@@ -5805,16 +5826,16 @@
         <v>124</v>
       </c>
       <c r="D236" t="s">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="E236" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F236" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="237" spans="1:6">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>54</v>
       </c>
@@ -5825,16 +5846,16 @@
         <v>122</v>
       </c>
       <c r="D237" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E237" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F237" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="238" spans="1:6">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>54</v>
       </c>
@@ -5845,16 +5866,16 @@
         <v>118</v>
       </c>
       <c r="D238" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="E238" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F238" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="239" spans="1:6">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>55</v>
       </c>
@@ -5868,13 +5889,13 @@
         <v>135</v>
       </c>
       <c r="E239" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F239" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="240" spans="1:6">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>55</v>
       </c>
@@ -5885,16 +5906,16 @@
         <v>126</v>
       </c>
       <c r="D240" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E240" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F240" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>55</v>
       </c>
@@ -5905,16 +5926,16 @@
         <v>124</v>
       </c>
       <c r="D241" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E241" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F241" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>55</v>
       </c>
@@ -5928,13 +5949,13 @@
         <v>133</v>
       </c>
       <c r="E242" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F242" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>55</v>
       </c>
@@ -5945,16 +5966,16 @@
         <v>118</v>
       </c>
       <c r="D243" t="s">
-        <v>205</v>
+        <v>134</v>
       </c>
       <c r="E243" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F243" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>55</v>
       </c>
@@ -5965,16 +5986,16 @@
         <v>127</v>
       </c>
       <c r="D244" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E244" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F244" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>56</v>
       </c>
@@ -5988,13 +6009,13 @@
         <v>135</v>
       </c>
       <c r="E245" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F245" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>56</v>
       </c>
@@ -6005,16 +6026,16 @@
         <v>121</v>
       </c>
       <c r="D246" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E246" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F246" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>56</v>
       </c>
@@ -6025,16 +6046,16 @@
         <v>126</v>
       </c>
       <c r="D247" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E247" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F247" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>56</v>
       </c>
@@ -6048,13 +6069,13 @@
         <v>133</v>
       </c>
       <c r="E248" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F248" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>56</v>
       </c>
@@ -6065,16 +6086,16 @@
         <v>118</v>
       </c>
       <c r="D249" t="s">
-        <v>206</v>
+        <v>134</v>
       </c>
       <c r="E249" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F249" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>57</v>
       </c>
@@ -6088,13 +6109,13 @@
         <v>135</v>
       </c>
       <c r="E250" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F250" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>57</v>
       </c>
@@ -6108,13 +6129,13 @@
         <v>132</v>
       </c>
       <c r="E251" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F251" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>57</v>
       </c>
@@ -6125,16 +6146,16 @@
         <v>125</v>
       </c>
       <c r="D252" t="s">
-        <v>207</v>
+        <v>141</v>
       </c>
       <c r="E252" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F252" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>57</v>
       </c>
@@ -6145,16 +6166,16 @@
         <v>118</v>
       </c>
       <c r="D253" t="s">
-        <v>208</v>
+        <v>134</v>
       </c>
       <c r="E253" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F253" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>57</v>
       </c>
@@ -6165,16 +6186,16 @@
         <v>128</v>
       </c>
       <c r="D254" t="s">
-        <v>209</v>
+        <v>162</v>
       </c>
       <c r="E254" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F254" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>58</v>
       </c>
@@ -6185,16 +6206,16 @@
         <v>123</v>
       </c>
       <c r="D255" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E255" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F255" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>58</v>
       </c>
@@ -6208,13 +6229,13 @@
         <v>132</v>
       </c>
       <c r="E256" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F256" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>58</v>
       </c>
@@ -6225,16 +6246,16 @@
         <v>126</v>
       </c>
       <c r="D257" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E257" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F257" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>58</v>
       </c>
@@ -6245,16 +6266,16 @@
         <v>125</v>
       </c>
       <c r="D258" t="s">
-        <v>210</v>
+        <v>141</v>
       </c>
       <c r="E258" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F258" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>58</v>
       </c>
@@ -6265,16 +6286,16 @@
         <v>118</v>
       </c>
       <c r="D259" t="s">
-        <v>211</v>
+        <v>134</v>
       </c>
       <c r="E259" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="F259" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>59</v>
       </c>
@@ -6288,13 +6309,13 @@
         <v>132</v>
       </c>
       <c r="E260" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F260" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>59</v>
       </c>
@@ -6305,16 +6326,16 @@
         <v>126</v>
       </c>
       <c r="D261" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E261" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F261" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>59</v>
       </c>
@@ -6328,13 +6349,13 @@
         <v>133</v>
       </c>
       <c r="E262" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F262" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>59</v>
       </c>
@@ -6345,16 +6366,16 @@
         <v>118</v>
       </c>
       <c r="D263" t="s">
-        <v>212</v>
+        <v>134</v>
       </c>
       <c r="E263" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F263" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>60</v>
       </c>
@@ -6368,13 +6389,13 @@
         <v>132</v>
       </c>
       <c r="E264" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F264" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>60</v>
       </c>
@@ -6385,16 +6406,16 @@
         <v>126</v>
       </c>
       <c r="D265" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E265" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F265" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>60</v>
       </c>
@@ -6408,13 +6429,13 @@
         <v>133</v>
       </c>
       <c r="E266" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F266" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>60</v>
       </c>
@@ -6425,16 +6446,16 @@
         <v>118</v>
       </c>
       <c r="D267" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="E267" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F267" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>60</v>
       </c>
@@ -6445,13 +6466,13 @@
         <v>131</v>
       </c>
       <c r="D268" t="s">
-        <v>213</v>
+        <v>163</v>
       </c>
       <c r="E268" t="s">
-        <v>217</v>
+        <v>168</v>
       </c>
       <c r="F268" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
